--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week02_07Sep.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week02_07Sep.xlsx
@@ -207,7 +207,7 @@
   </si>
   <si>
     <t xml:space="preserve">TA leads a small group for sensitive content and pre-agrees with the safeguarding lead how any disclosures are handled.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: feeds each pupil's real destination (college/barbering) → PfA plan and IEDP Outcome 5 [NS].</t>
